--- a/data/golfdaten.xlsx
+++ b/data/golfdaten.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8062010bbf1bb3b7/Dokumente/GitHub/GolfApp/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8062010bbf1bb3b7/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{FE24B12B-A094-45EE-AADB-599D72074745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74685C72-CEA3-42BE-A51B-251411D961AD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8B09F41-CFC0-410A-96D0-E68FD245D6EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21210" yWindow="3810" windowWidth="18240" windowHeight="10605" xr2:uid="{3B056965-1182-4BC6-8176-35AB36783349}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3B056965-1182-4BC6-8176-35AB36783349}"/>
   </bookViews>
   <sheets>
-    <sheet name="Alle Daten" sheetId="2" r:id="rId1"/>
+    <sheet name="22.07.26" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alle Daten'!$A$1:$F$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'22.07.26'!$A$1:$F$287</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
